--- a/static/excel/SOFI_model.xlsx
+++ b/static/excel/SOFI_model.xlsx
@@ -7870,16 +7870,16 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="55" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B46" s="56">
-        <f>B8*B29+B9*B39*(1-B43)</f>
+        <f>MAX(0.085, B8*B29+B9*B39*(1-B43))</f>
         <v/>
       </c>
       <c r="C46" s="57" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10127,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="119" t="inlineStr">
         <is>
-          <t>JS SCORECARD — SOFI  |  Master Prompt v2  |  23 May 2026  |  Sector bucket: Bank</t>
+          <t>JS SCORECARD — SOFI  |  Master Prompt v2  |  24 May 2026  |  Sector bucket: Bank</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="D22" s="135" t="inlineStr">
         <is>
-          <t>Current 62.6x  |  5yr avg 47.5x  [+32% vs benchmark]  [trail=2.19 | no_fwd_data(fallback) | abs=0.0 → blended 40/40/20=1.75]  PEG≈159.10 (trailing_pe=62.6x / rev_cagr=39%, revenue proxy)</t>
+          <t>Current 62.6x  |  5yr avg 47.5x  [+32% vs benchmark]  [trail=2.19 | fwd_pe=26.0x→10.00 | abs=0.0 → blended 40/40/20=4.87]  PEG=59.38 (fwd_pe=26.0x / eps_growth=44%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
       <c r="E22" s="136" t="inlineStr">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="F22" s="137" t="n">
-        <v>1.75</v>
+        <v>5.37</v>
       </c>
       <c r="G22" s="138">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="H22" s="139" t="inlineStr">
         <is>
-          <t>Current 62.6x  |  5yr avg 47.5x  [+32% vs benchmark]  [trail=2.19 | no_fwd_data(fallback) | abs=0.0 → blended 40/40/20=1.75]  PEG≈159.10 (trailing_pe=62.6x / rev_cagr=39%, revenue proxy)</t>
+          <t>Current 62.6x  |  5yr avg 47.5x  [+32% vs benchmark]  [trail=2.19 | fwd_pe=26.0x→10.00 | abs=0.0 → blended 40/40/20=4.87]  PEG=59.38 (fwd_pe=26.0x / eps_growth=44%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>

--- a/static/excel/SOFI_model.xlsx
+++ b/static/excel/SOFI_model.xlsx
@@ -39,7 +39,7 @@
     <numFmt numFmtId="175" formatCode="0.000"/>
     <numFmt numFmtId="176" formatCode="0.00;(0.00);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -241,18 +241,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001565C0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00E65100"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00B71C1C"/>
       <sz val="11"/>
     </font>
@@ -262,7 +250,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -364,11 +352,6 @@
         <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -396,7 +379,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -810,12 +793,6 @@
     <xf numFmtId="0" fontId="33" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -826,17 +803,17 @@
     <xf numFmtId="0" fontId="32" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="36" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="34" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -7480,11 +7457,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7472,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7762,11 +7739,11 @@
         </is>
       </c>
       <c r="B36" s="46" t="n">
-        <v>0.1657</v>
+        <v>0.1656</v>
       </c>
       <c r="C36" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 12.00%</t>
+          <t>Rf 4.56% + spread 12.00%</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7782,7 @@
         </is>
       </c>
       <c r="B39" s="48" t="n">
-        <v>0.3184</v>
+        <v>0.3183</v>
       </c>
       <c r="C39" s="49" t="inlineStr">
         <is>
@@ -9511,7 +9488,7 @@
         </is>
       </c>
       <c r="B38" s="106" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C38" s="104" t="n"/>
       <c r="D38" s="104" t="n"/>
@@ -9525,7 +9502,7 @@
       <c r="L38" s="104" t="n"/>
       <c r="M38" s="76" t="inlineStr">
         <is>
-          <t>Growth tier: HIGH (40.3% 3yr avg rev growth).  Bear 14x / Base 18x / Bull 22x.  Override manually if needed.</t>
+          <t>Growth tier: HIGH (40.3% 3yr avg rev growth).  Bear 22x / Base 28x / Bull 32x.  Override manually if needed.</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -10127,7 +10104,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="119" t="inlineStr">
         <is>
-          <t>JS SCORECARD — SOFI  |  Master Prompt v2  |  24 May 2026  |  Sector bucket: Bank</t>
+          <t>JS SCORECARD — SOFI  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Bank</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10203,7 @@
         </is>
       </c>
       <c r="C8" s="126" t="n">
-        <v>0.025</v>
+        <v>0.075</v>
       </c>
       <c r="D8" s="127" t="inlineStr">
         <is>
@@ -10256,11 +10233,11 @@
         </is>
       </c>
       <c r="C9" s="134" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D9" s="135" t="inlineStr">
         <is>
-          <t>GM 75.1% ✓ (&gt;40%)  |  GM trend -11.1% ✗ (&gt;+1pp)  |  ROIC-WACC -9.7% ✗ (&gt;+5pp)  |  Rev consistency σ=17.5% ✗ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
+          <t>GM 75.1% ✓ (&gt;40%)  |  GM trend -11.1% ✗ (&gt;+1pp)  |  ROIC-WACC -9.6% ✗ (&gt;+5pp)  |  Rev consistency σ=17.5% ✗ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E9" s="136" t="inlineStr">
@@ -10277,7 +10254,7 @@
       </c>
       <c r="H9" s="139" t="inlineStr">
         <is>
-          <t>GM 75.1% ✓ (&gt;40%)  |  GM trend -11.1% ✗ (&gt;+1pp)  |  ROIC-WACC -9.7% ✗ (&gt;+5pp)  |  Rev consistency σ=17.5% ✗ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
+          <t>GM 75.1% ✓ (&gt;40%)  |  GM trend -11.1% ✗ (&gt;+1pp)  |  ROIC-WACC -9.6% ✗ (&gt;+5pp)  |  Rev consistency σ=17.5% ✗ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10293,7 +10270,7 @@
         </is>
       </c>
       <c r="C10" s="126" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="D10" s="127" t="inlineStr">
         <is>
@@ -10323,7 +10300,7 @@
         </is>
       </c>
       <c r="C11" s="134" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="D11" s="135" t="inlineStr">
         <is>
@@ -10367,7 +10344,7 @@
         </is>
       </c>
       <c r="C13" s="134" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="D13" s="135" t="inlineStr">
         <is>
@@ -10393,51 +10370,21 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cash Quality  (FCF / Net Income)</t>
-        </is>
-      </c>
-      <c r="B14" s="133" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C14" s="134" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D14" s="135" t="inlineStr">
-        <is>
-          <t>-493%  [trend penalty: declined &gt;15pp vs 3yr ago]  [through-cycle: 70/30 latest+5yr median, latest -827.9% → smoothed -492.6%]  [QoE: Sloan accruals +11.9% 3yr avg — high]</t>
-        </is>
-      </c>
-      <c r="E14" s="141" t="inlineStr">
-        <is>
-          <t>MOD-HIGH</t>
-        </is>
-      </c>
-      <c r="F14" s="137" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G14" s="138">
-        <f>IF(F14="",0,C14*F14*10)</f>
-        <v/>
-      </c>
-      <c r="H14" s="139" t="inlineStr">
-        <is>
-          <t>-493%  [trend penalty: declined &gt;15pp vs 3yr ago]  [through-cycle: 70/30 latest+5yr median, latest -827.9% → smoothed -492.6%]  [QoE: Sloan accruals +11.9% 3yr avg — high]</t>
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>PART 3 — RISK PROFILE  (quantitative / qualitative)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="132" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capital Returns</t>
+          <t xml:space="preserve">  Credit Risk  (D / EBITDA)</t>
         </is>
       </c>
       <c r="B15" s="133" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="C15" s="134" t="n">
@@ -10445,16 +10392,16 @@
       </c>
       <c r="D15" s="135" t="inlineStr">
         <is>
-          <t>$65mm latest FY — only 2/5yr history  [FCF negative — capital returns funded externally]</t>
-        </is>
-      </c>
-      <c r="E15" s="142" t="inlineStr">
-        <is>
-          <t>MOD-LOW</t>
+          <t>Net cash $3,114mm — no net leverage  [through-cycle: 70/30 latest+5yr median, latest 2.4x → smoothed 3.1x]</t>
+        </is>
+      </c>
+      <c r="E15" s="140" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F15" s="137" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="G15" s="138">
         <f>IF(F15="",0,C15*F15*10)</f>
@@ -10462,36 +10409,36 @@
       </c>
       <c r="H15" s="139" t="inlineStr">
         <is>
-          <t>$65mm latest FY — only 2/5yr history  [FCF negative — capital returns funded externally]</t>
+          <t>Net cash $3,114mm — no net leverage  [through-cycle: 70/30 latest+5yr median, latest 2.4x → smoothed 3.1x]</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="132" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROIC</t>
+          <t xml:space="preserve">  Execution Risk</t>
         </is>
       </c>
       <c r="B16" s="133" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="C16" s="134" t="n">
-        <v>0.075</v>
+        <v>0.05</v>
       </c>
       <c r="D16" s="135" t="inlineStr">
         <is>
-          <t>5.7%  [through-cycle: 70/30 latest+5yr median, latest 6.5% → smoothed 5.7%]</t>
-        </is>
-      </c>
-      <c r="E16" s="142" t="inlineStr">
-        <is>
-          <t>MOD-LOW</t>
+          <t>Rev growth σ=17.5%  |  OM trend -33.2%, σ=13.7%  [quality = direction + stability]</t>
+        </is>
+      </c>
+      <c r="E16" s="136" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F16" s="137" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="G16" s="138">
         <f>IF(F16="",0,C16*F16*10)</f>
@@ -10499,301 +10446,101 @@
       </c>
       <c r="H16" s="139" t="inlineStr">
         <is>
-          <t>5.7%  [through-cycle: 70/30 latest+5yr median, latest 6.5% → smoothed 5.7%]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>PART 3 — RISK PROFILE  (quantitative / qualitative)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Credit Risk  (D / EBITDA)</t>
-        </is>
-      </c>
-      <c r="B18" s="133" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C18" s="134" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D18" s="135" t="inlineStr">
-        <is>
-          <t>Net cash $3,114mm — no net leverage  [through-cycle: 70/30 latest+5yr median, latest 2.4x → smoothed 3.1x]</t>
-        </is>
-      </c>
-      <c r="E18" s="140" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F18" s="137" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" s="138">
-        <f>IF(F18="",0,C18*F18*10)</f>
-        <v/>
-      </c>
-      <c r="H18" s="139" t="inlineStr">
-        <is>
-          <t>Net cash $3,114mm — no net leverage  [through-cycle: 70/30 latest+5yr median, latest 2.4x → smoothed 3.1x]</t>
+          <t>Rev growth σ=17.5%  |  OM trend -33.2%, σ=13.7%  [quality = direction + stability]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="n"/>
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="42" t="n"/>
+      <c r="D17" s="42" t="n"/>
+      <c r="E17" s="42" t="n"/>
+      <c r="F17" s="42" t="n"/>
+      <c r="G17" s="42" t="n"/>
+      <c r="H17" s="42" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="141" t="inlineStr">
+        <is>
+          <t>TOTAL SCORE  (max = 100.0)</t>
+        </is>
+      </c>
+      <c r="B18" s="142" t="n"/>
+      <c r="C18" s="142" t="n"/>
+      <c r="D18" s="142" t="n"/>
+      <c r="E18" s="142" t="n"/>
+      <c r="F18" s="142" t="n"/>
+      <c r="G18" s="143">
+        <f>G8+G9+G10+G11+G13+G15+G16</f>
+        <v/>
+      </c>
+      <c r="H18" s="144" t="inlineStr">
+        <is>
+          <t>Floor cap 89.8 applies — see gate warning above.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Interest Cover  (EBIT / Interest)</t>
-        </is>
-      </c>
-      <c r="B19" s="133" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C19" s="134" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="D19" s="135" t="inlineStr">
-        <is>
-          <t>0.5x</t>
-        </is>
-      </c>
-      <c r="E19" s="136" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F19" s="137" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G19" s="138">
-        <f>IF(F19="",0,C19*F19*10)</f>
-        <v/>
-      </c>
-      <c r="H19" s="139" t="inlineStr">
-        <is>
-          <t>0.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Execution Risk</t>
-        </is>
-      </c>
-      <c r="B20" s="133" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C20" s="134" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D20" s="135" t="inlineStr">
-        <is>
-          <t>Rev growth σ=17.5%  |  OM trend -33.2%, σ=13.7%  [quality = direction + stability]</t>
-        </is>
-      </c>
-      <c r="E20" s="136" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F20" s="137" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="138">
-        <f>IF(F20="",0,C20*F20*10)</f>
-        <v/>
-      </c>
-      <c r="H20" s="139" t="inlineStr">
-        <is>
-          <t>Rev growth σ=17.5%  |  OM trend -33.2%, σ=13.7%  [quality = direction + stability]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>PART 4 — VALUATION  (qualitative / user-supplied market data)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Valuation vs Median  (P/E)</t>
-        </is>
-      </c>
-      <c r="B22" s="133" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="C22" s="134" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D22" s="135" t="inlineStr">
-        <is>
-          <t>Current 62.6x  |  5yr avg 47.5x  [+32% vs benchmark]  [trail=2.19 | fwd_pe=26.0x→10.00 | abs=0.0 → blended 40/40/20=4.87]  PEG=59.38 (fwd_pe=26.0x / eps_growth=44%)  [revision:Strong upgrade cycle→+0.50]</t>
-        </is>
-      </c>
-      <c r="E22" s="136" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F22" s="137" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="G22" s="138">
-        <f>IF(F22="",0,C22*F22*10)</f>
-        <v/>
-      </c>
-      <c r="H22" s="139" t="inlineStr">
-        <is>
-          <t>Current 62.6x  |  5yr avg 47.5x  [+32% vs benchmark]  [trail=2.19 | fwd_pe=26.0x→10.00 | abs=0.0 → blended 40/40/20=4.87]  PEG=59.38 (fwd_pe=26.0x / eps_growth=44%)  [revision:Strong upgrade cycle→+0.50]</t>
-        </is>
-      </c>
+      <c r="A19" s="145" t="inlineStr">
+        <is>
+          <t>FLOOR-ADJUSTED SCORE  (capped at 89.8)</t>
+        </is>
+      </c>
+      <c r="B19" s="146" t="n"/>
+      <c r="C19" s="146" t="n"/>
+      <c r="D19" s="146" t="n"/>
+      <c r="E19" s="146" t="n"/>
+      <c r="F19" s="146" t="n"/>
+      <c r="G19" s="147">
+        <f>MIN(G18,89.8)</f>
+        <v/>
+      </c>
+      <c r="H19" s="146" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="n"/>
+      <c r="B20" s="42" t="n"/>
+      <c r="C20" s="42" t="n"/>
+      <c r="D20" s="42" t="n"/>
+      <c r="E20" s="42" t="n"/>
+      <c r="F20" s="42" t="n"/>
+      <c r="G20" s="42" t="n"/>
+      <c r="H20" s="42" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="148">
+        <f>IF(G19="","Score incomplete — fill qualitative tiers above",IF(G19&gt;=80,"STRONG BUY",IF(G19&gt;=65,"BUY",IF(G19&gt;=50,"HOLD",IF(G19&gt;=35,"REDUCE","SELL")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="n"/>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="42" t="n"/>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="42" t="n"/>
+      <c r="G22" s="42" t="n"/>
+      <c r="H22" s="42" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Valuation vs Median  (P/FCF)</t>
-        </is>
-      </c>
-      <c r="B23" s="133" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="C23" s="134" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D23" s="135" t="inlineStr">
-        <is>
-          <t>Current -7.6x — P/FCF negative (earnings/FCF below zero, multiple meaningless)</t>
-        </is>
-      </c>
-      <c r="E23" s="136" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F23" s="137" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="138">
-        <f>IF(F23="",0,C23*F23*10)</f>
-        <v/>
-      </c>
-      <c r="H23" s="139" t="inlineStr">
-        <is>
-          <t>Current -7.6x — P/FCF negative (earnings/FCF below zero, multiple meaningless)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="42" t="n"/>
-      <c r="B24" s="42" t="n"/>
-      <c r="C24" s="42" t="n"/>
-      <c r="D24" s="42" t="n"/>
-      <c r="E24" s="42" t="n"/>
-      <c r="F24" s="42" t="n"/>
-      <c r="G24" s="42" t="n"/>
-      <c r="H24" s="42" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="143" t="inlineStr">
-        <is>
-          <t>TOTAL SCORE  (max = 100.0)</t>
-        </is>
-      </c>
-      <c r="B25" s="144" t="n"/>
-      <c r="C25" s="144" t="n"/>
-      <c r="D25" s="144" t="n"/>
-      <c r="E25" s="144" t="n"/>
-      <c r="F25" s="144" t="n"/>
-      <c r="G25" s="145">
-        <f>G8+G9+G10+G11+G13+G14+G15+G16+G18+G19+G20+G22+G23</f>
-        <v/>
-      </c>
-      <c r="H25" s="146" t="inlineStr">
-        <is>
-          <t>Floor cap 89.8 applies — see gate warning above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="147" t="inlineStr">
-        <is>
-          <t>FLOOR-ADJUSTED SCORE  (capped at 89.8)</t>
-        </is>
-      </c>
-      <c r="B26" s="148" t="n"/>
-      <c r="C26" s="148" t="n"/>
-      <c r="D26" s="148" t="n"/>
-      <c r="E26" s="148" t="n"/>
-      <c r="F26" s="148" t="n"/>
-      <c r="G26" s="149">
-        <f>MIN(G25,89.8)</f>
-        <v/>
-      </c>
-      <c r="H26" s="148" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="42" t="n"/>
-      <c r="B27" s="42" t="n"/>
-      <c r="C27" s="42" t="n"/>
-      <c r="D27" s="42" t="n"/>
-      <c r="E27" s="42" t="n"/>
-      <c r="F27" s="42" t="n"/>
-      <c r="G27" s="42" t="n"/>
-      <c r="H27" s="42" t="n"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="150">
-        <f>IF(G26="","Score incomplete — fill qualitative tiers above",IF(G26&gt;=80,"STRONG BUY",IF(G26&gt;=65,"BUY",IF(G26&gt;=50,"HOLD",IF(G26&gt;=35,"REDUCE","SELL")))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="42" t="n"/>
-      <c r="B29" s="42" t="n"/>
-      <c r="C29" s="42" t="n"/>
-      <c r="D29" s="42" t="n"/>
-      <c r="E29" s="42" t="n"/>
-      <c r="F29" s="42" t="n"/>
-      <c r="G29" s="42" t="n"/>
-      <c r="H29" s="42" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="151" t="inlineStr">
+      <c r="A23" s="149" t="inlineStr">
         <is>
           <t>SCORING GUIDE:  ≥80 STRONG BUY  |  65–79 BUY  |  50–64 HOLD  |  35–49 REDUCE  |  &lt;35 SELL    ||  Soft cap (non-banks only): −5pts per 1.0x of D/EBITDA above 3.0x; −4pts per 1.0x of EBIT/Int below 3.0x; min 40    ||  Banks: gates exempt; P3 uses Equity/Assets (CET1 proxy) instead of D/EBITDA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E9:E50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
